--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00868</v>
+        <v>0.0563</v>
       </c>
       <c r="E2">
-        <v>-0.116</v>
+        <v>0.156</v>
       </c>
       <c r="G2">
-        <v>-0.3330074992745101</v>
+        <v>-0.317602569104715</v>
       </c>
       <c r="H2">
-        <v>-0.3330074992745101</v>
+        <v>-0.317602569104715</v>
       </c>
       <c r="I2">
-        <v>-0.4248316099766316</v>
+        <v>-0.4187040427383775</v>
       </c>
       <c r="J2">
-        <v>-0.3861217264417165</v>
+        <v>-0.3975650605238765</v>
       </c>
       <c r="K2">
-        <v>-293.891</v>
+        <v>-292.127</v>
       </c>
       <c r="L2">
-        <v>-0.4488735814763338</v>
+        <v>-0.4383790029712777</v>
       </c>
       <c r="M2">
-        <v>11.6158</v>
+        <v>16.0776</v>
       </c>
       <c r="N2">
-        <v>0.02041082410824108</v>
+        <v>0.0320782122905028</v>
       </c>
       <c r="O2">
-        <v>-0.03952417733105131</v>
+        <v>-0.05503633693564785</v>
       </c>
       <c r="P2">
-        <v>11.6158</v>
+        <v>16.0776</v>
       </c>
       <c r="Q2">
-        <v>0.02041082410824108</v>
+        <v>0.0320782122905028</v>
       </c>
       <c r="R2">
-        <v>-0.03952417733105131</v>
+        <v>-0.05503633693564785</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>564.3100000000001</v>
+        <v>480.79</v>
       </c>
       <c r="V2">
-        <v>0.9915832015463012</v>
+        <v>0.9592777334397447</v>
       </c>
       <c r="W2">
-        <v>-0.06617888714757392</v>
+        <v>-0.06989959563561153</v>
       </c>
       <c r="X2">
-        <v>0.09048319142839241</v>
+        <v>0.136101406900087</v>
       </c>
       <c r="Y2">
-        <v>-0.1566620785759663</v>
+        <v>-0.2060010025356986</v>
       </c>
       <c r="Z2">
-        <v>-1.640088776665565</v>
+        <v>7.314016024585666</v>
       </c>
       <c r="AA2">
-        <v>-0.001162242590931895</v>
+        <v>-0.04346806046387313</v>
       </c>
       <c r="AB2">
-        <v>0.09048319142839241</v>
+        <v>0.13608654480378</v>
       </c>
       <c r="AC2">
-        <v>-0.09164651350820777</v>
+        <v>-0.1787595310800013</v>
       </c>
       <c r="AD2">
-        <v>23.58</v>
+        <v>23.417</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.58</v>
+        <v>23.417</v>
       </c>
       <c r="AG2">
-        <v>-540.73</v>
+        <v>-457.373</v>
       </c>
       <c r="AH2">
-        <v>0.0397853816562057</v>
+        <v>0.0446363728205529</v>
       </c>
       <c r="AI2">
-        <v>0.09995337204866263</v>
+        <v>0.1155841399428422</v>
       </c>
       <c r="AJ2">
-        <v>-19.05992245329573</v>
+        <v>-10.4358728637598</v>
       </c>
       <c r="AK2">
-        <v>1.646559074299635</v>
+        <v>1.644085221411035</v>
       </c>
       <c r="AL2">
-        <v>0.199</v>
+        <v>0.283</v>
       </c>
       <c r="AM2">
-        <v>0.199</v>
+        <v>0.283</v>
       </c>
       <c r="AN2">
-        <v>-0.08671126032867905</v>
+        <v>-0.08620759475030833</v>
       </c>
       <c r="AO2">
-        <v>-1397.738693467337</v>
+        <v>-985.922261484099</v>
       </c>
       <c r="AP2">
-        <v>1.988438498622843</v>
+        <v>1.683777863677361</v>
       </c>
       <c r="AQ2">
-        <v>-1397.738693467337</v>
+        <v>-985.922261484099</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rupali Life Insurance Company Limited (DSE:RUPALILIFE)</t>
+          <t>Sonali Life Insurance Company Limited (DSE:SONALILIFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1387931034482759</v>
+        <v>0.3737769080234834</v>
       </c>
       <c r="H3">
-        <v>0.1387931034482759</v>
+        <v>0.3737769080234834</v>
       </c>
       <c r="I3">
-        <v>0.08534482758620691</v>
+        <v>0.4970645792563601</v>
       </c>
       <c r="J3">
-        <v>0.06775546677880574</v>
+        <v>0.4937775392967615</v>
       </c>
       <c r="K3">
-        <v>1.95</v>
+        <v>24.6</v>
       </c>
       <c r="L3">
-        <v>0.05603448275862069</v>
+        <v>0.4814090019569472</v>
       </c>
       <c r="M3">
-        <v>0.398</v>
+        <v>0.189</v>
       </c>
       <c r="N3">
-        <v>0.01868544600938967</v>
+        <v>0.006872727272727273</v>
       </c>
       <c r="O3">
-        <v>0.2041025641025641</v>
+        <v>0.007682926829268293</v>
       </c>
       <c r="P3">
-        <v>0.398</v>
+        <v>0.189</v>
       </c>
       <c r="Q3">
-        <v>0.01868544600938967</v>
+        <v>0.006872727272727273</v>
       </c>
       <c r="R3">
-        <v>0.2041025641025641</v>
+        <v>0.007682926829268293</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,52 +764,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>20.8</v>
+        <v>15.1</v>
       </c>
       <c r="V3">
-        <v>0.9765258215962441</v>
+        <v>0.5490909090909091</v>
+      </c>
+      <c r="W3">
+        <v>4.263431542461006</v>
       </c>
       <c r="X3">
-        <v>0.09048319142839241</v>
+        <v>0.1384227410679704</v>
+      </c>
+      <c r="Y3">
+        <v>4.125008801393035</v>
       </c>
       <c r="AB3">
-        <v>0.09048319142839241</v>
+        <v>0.1360521149800301</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.978</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.978</v>
       </c>
       <c r="AG3">
-        <v>-20.8</v>
+        <v>-14.122</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.03434229931877238</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.1675231243576567</v>
       </c>
       <c r="AJ3">
-        <v>-41.6</v>
+        <v>-1.055613694124682</v>
       </c>
       <c r="AK3">
-        <v>1.759729272419628</v>
+        <v>1.524724681494278</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.03595588235294118</v>
+      </c>
+      <c r="AO3">
+        <v>373.5294117647059</v>
       </c>
       <c r="AP3">
-        <v>-6.227544910179641</v>
+        <v>-0.5191911764705882</v>
+      </c>
+      <c r="AQ3">
+        <v>373.5294117647059</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fareast Islami Life Insurance Company Limited (DSE:FAREASTLIF)</t>
+          <t>Chartered Life Insurance Company Limited (DSE:CLICL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,118 +841,91 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.04269999999999999</v>
+        <v>0.463</v>
+      </c>
+      <c r="E4">
+        <v>0.736</v>
       </c>
       <c r="G4">
-        <v>-2.553431798436142</v>
+        <v>0.2980030721966206</v>
       </c>
       <c r="H4">
-        <v>-2.553431798436142</v>
+        <v>0.2980030721966206</v>
       </c>
       <c r="I4">
-        <v>-2.84622067767159</v>
+        <v>0.2749615975422427</v>
       </c>
       <c r="J4">
-        <v>-2.84622067767159</v>
+        <v>0.2587211756991044</v>
       </c>
       <c r="K4">
-        <v>-330.6</v>
+        <v>1.61</v>
       </c>
       <c r="L4">
-        <v>-2.87228496959166</v>
+        <v>0.2473118279569893</v>
       </c>
       <c r="M4">
-        <v>0.881</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.01874468085106383</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.002664851784633999</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.881</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01874468085106383</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.002664851784633999</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.436170212765957</v>
-      </c>
-      <c r="W4">
-        <v>-37.5255391600454</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.100042822635011</v>
-      </c>
-      <c r="Y4">
-        <v>-37.62558198268042</v>
-      </c>
-      <c r="Z4">
-        <v>-2.009076627683715</v>
-      </c>
-      <c r="AA4">
-        <v>5.718275440740095</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="AB4">
-        <v>0.08998227783242041</v>
-      </c>
-      <c r="AC4">
-        <v>5.628293162907675</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="AD4">
-        <v>8.83</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8.83</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-58.67</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.1581586960415547</v>
-      </c>
-      <c r="AI4">
-        <v>0.4856985698569857</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>5.027420736932305</v>
-      </c>
-      <c r="AK4">
-        <v>1.189578264395783</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0.02711083819465766</v>
-      </c>
-      <c r="AO4">
-        <v>-5118.75</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.1801350936444581</v>
-      </c>
-      <c r="AQ4">
-        <v>-5118.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunlife Insurance Company Limited (DSE:SUNLIFEINS)</t>
+          <t>National Life Insurance Company Limited (DSE:NATLIFEINS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,43 +945,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0638</v>
+        <v>0.125</v>
+      </c>
+      <c r="E5">
+        <v>0.431</v>
       </c>
       <c r="G5">
-        <v>-0.02007751937984496</v>
+        <v>0.2900150526843954</v>
       </c>
       <c r="H5">
-        <v>-0.02007751937984496</v>
+        <v>0.2900150526843954</v>
       </c>
       <c r="I5">
-        <v>-0.09302325581395349</v>
+        <v>0.2553938785750125</v>
       </c>
       <c r="J5">
-        <v>-0.09302325581395349</v>
+        <v>0.2326115837248551</v>
       </c>
       <c r="K5">
-        <v>-1.42</v>
+        <v>48</v>
       </c>
       <c r="L5">
-        <v>-0.1100775193798449</v>
+        <v>0.2408429503261415</v>
       </c>
       <c r="M5">
-        <v>0.0358</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N5">
-        <v>0.002503496503496503</v>
+        <v>0.04568554790894654</v>
       </c>
       <c r="O5">
-        <v>-0.0252112676056338</v>
+        <v>0.1797916666666667</v>
       </c>
       <c r="P5">
-        <v>0.0358</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.002503496503496503</v>
+        <v>0.04568554790894654</v>
       </c>
       <c r="R5">
-        <v>-0.0252112676056338</v>
+        <v>0.1797916666666667</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,67 +993,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>8.449999999999999</v>
+        <v>215</v>
       </c>
       <c r="V5">
-        <v>0.5909090909090908</v>
+        <v>1.138168343038645</v>
       </c>
       <c r="W5">
-        <v>-0.3364928909952606</v>
+        <v>2.823529411764706</v>
       </c>
       <c r="X5">
-        <v>0.09080343820316689</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="Y5">
-        <v>-0.4272963291984275</v>
-      </c>
-      <c r="Z5">
-        <v>-23.71323529411763</v>
-      </c>
-      <c r="AA5">
-        <v>2.205882352941174</v>
+        <v>2.687442096911298</v>
       </c>
       <c r="AB5">
-        <v>0.09046338293434038</v>
-      </c>
-      <c r="AC5">
-        <v>2.115418970006834</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="AD5">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-8.359999999999999</v>
+        <v>-215</v>
       </c>
       <c r="AH5">
-        <v>0.006254343293954134</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.02093023255813953</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-1.407407407407407</v>
+        <v>8.237547892720308</v>
       </c>
       <c r="AK5">
-        <v>2.014457831325301</v>
+        <v>1.076614922383575</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AN5">
-        <v>-0.254957507082153</v>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>613.2530120481928</v>
       </c>
       <c r="AP5">
-        <v>23.68271954674221</v>
+        <v>-4.174757281553398</v>
+      </c>
+      <c r="AQ5">
+        <v>613.2530120481928</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prime Islami Life Insurance Limited (DSE:PRIMELIFE)</t>
+          <t>Pragati Life Insurance Limited (DSE:PRAGATILIF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,43 +1070,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0717</v>
+        <v>0.132</v>
+      </c>
+      <c r="E6">
+        <v>-0.161</v>
       </c>
       <c r="G6">
-        <v>-0.06947162426614481</v>
+        <v>0.06431535269709543</v>
       </c>
       <c r="H6">
-        <v>-0.06947162426614481</v>
+        <v>0.06431535269709543</v>
       </c>
       <c r="I6">
-        <v>-0.1103718199608611</v>
+        <v>0.06141078838174274</v>
       </c>
       <c r="J6">
-        <v>-0.1103718199608611</v>
+        <v>0.05098211995473406</v>
       </c>
       <c r="K6">
-        <v>-7.64</v>
+        <v>2.29</v>
       </c>
       <c r="L6">
-        <v>-0.1495107632093933</v>
+        <v>0.0475103734439834</v>
       </c>
       <c r="M6">
-        <v>1.31</v>
+        <v>0.327</v>
       </c>
       <c r="N6">
-        <v>0.06359223300970873</v>
+        <v>0.008493506493506494</v>
       </c>
       <c r="O6">
-        <v>-0.1714659685863874</v>
+        <v>0.1427947598253275</v>
       </c>
       <c r="P6">
-        <v>1.31</v>
+        <v>0.327</v>
       </c>
       <c r="Q6">
-        <v>0.06359223300970873</v>
+        <v>0.008493506493506494</v>
       </c>
       <c r="R6">
-        <v>-0.1714659685863874</v>
+        <v>0.1427947598253275</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,31 +1118,22 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>8.09</v>
+        <v>16.8</v>
       </c>
       <c r="V6">
-        <v>0.3927184466019417</v>
+        <v>0.4363636363636364</v>
       </c>
       <c r="W6">
-        <v>-2.116343490304709</v>
+        <v>0.506637168141593</v>
       </c>
       <c r="X6">
-        <v>0.09048319142839241</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="Y6">
-        <v>-2.206826681733101</v>
-      </c>
-      <c r="Z6">
-        <v>-3.061713600958658</v>
-      </c>
-      <c r="AA6">
-        <v>0.3379269023367285</v>
+        <v>0.3705498532881853</v>
       </c>
       <c r="AB6">
-        <v>0.09048319142839241</v>
-      </c>
-      <c r="AC6">
-        <v>0.2474437109083361</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1166,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-8.09</v>
+        <v>-16.8</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1175,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.6466826538768984</v>
+        <v>-0.7741935483870969</v>
       </c>
       <c r="AK6">
-        <v>3.236</v>
+        <v>1.311475409836065</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1187,10 +1166,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.487132352941176</v>
+        <v>-5.490196078431373</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghna Life Insurance Company Limited (DSE:MEGHNALIFE)</t>
+          <t>Rupali Life Insurance Company Limited (DSE:RUPALILIFE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,43 +1189,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00389</v>
+        <v>0.0563</v>
+      </c>
+      <c r="E7">
+        <v>-0.119</v>
       </c>
       <c r="G7">
-        <v>0.2213114754098361</v>
+        <v>0.155363321799308</v>
       </c>
       <c r="H7">
-        <v>0.2213114754098361</v>
+        <v>0.155363321799308</v>
       </c>
       <c r="I7">
-        <v>-0.02557377049180328</v>
+        <v>0.09688581314878893</v>
       </c>
       <c r="J7">
-        <v>-0.02557377049180328</v>
+        <v>0.06964730164511625</v>
       </c>
       <c r="K7">
-        <v>-2.8</v>
+        <v>1.64</v>
       </c>
       <c r="L7">
-        <v>-0.04590163934426229</v>
+        <v>0.05674740484429066</v>
       </c>
       <c r="M7">
-        <v>0.783</v>
+        <v>0.371</v>
       </c>
       <c r="N7">
-        <v>0.0243167701863354</v>
+        <v>0.01592274678111588</v>
       </c>
       <c r="O7">
-        <v>-0.2796428571428572</v>
+        <v>0.226219512195122</v>
       </c>
       <c r="P7">
-        <v>0.783</v>
+        <v>0.371</v>
       </c>
       <c r="Q7">
-        <v>0.0243167701863354</v>
+        <v>0.01592274678111588</v>
       </c>
       <c r="R7">
-        <v>-0.2796428571428572</v>
+        <v>0.226219512195122</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1237,46 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>104.7</v>
+        <v>17.8</v>
       </c>
       <c r="V7">
-        <v>3.251552795031056</v>
+        <v>0.7639484978540773</v>
       </c>
       <c r="W7">
-        <v>-0.7088607594936708</v>
+        <v>0.1826280623608018</v>
       </c>
       <c r="X7">
-        <v>0.09048319142839241</v>
+        <v>0.1361154989467665</v>
       </c>
       <c r="Y7">
-        <v>-0.7993439509220632</v>
-      </c>
-      <c r="Z7">
-        <v>-0.6499733617474694</v>
-      </c>
-      <c r="AA7">
-        <v>0.01662226957911561</v>
+        <v>0.04651256341403529</v>
       </c>
       <c r="AB7">
-        <v>0.09048319142839241</v>
-      </c>
-      <c r="AC7">
-        <v>-0.0738609218492768</v>
+        <v>0.1360857747541524</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG7">
-        <v>-104.7</v>
+        <v>-17.79</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.000429000429000429</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.001310615989515072</v>
       </c>
       <c r="AJ7">
-        <v>1.444137931034483</v>
+        <v>-3.228675136116151</v>
       </c>
       <c r="AK7">
-        <v>1.039721946375372</v>
+        <v>1.749262536873156</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1312,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-0</v>
+        <v>0.003236245954692557</v>
       </c>
       <c r="AP7">
-        <v>84.43548387096774</v>
+        <v>-5.757281553398058</v>
       </c>
     </row>
     <row r="8">
@@ -1326,7 +1299,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Popular Life Insurance Company Limited (DSE:POPULARLIF)</t>
+          <t>Padma Islami Life Insurance Limited (DSE:PADMALIFE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1334,41 +1307,44 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.223</v>
+      </c>
       <c r="G8">
-        <v>0.1120331950207469</v>
+        <v>0.07622739018087854</v>
       </c>
       <c r="H8">
-        <v>0.1120331950207469</v>
+        <v>0.07622739018087854</v>
       </c>
       <c r="I8">
-        <v>0.0404564315352697</v>
+        <v>-0.1049095607235142</v>
       </c>
       <c r="J8">
-        <v>0.02022821576763485</v>
+        <v>-0.1049095607235142</v>
       </c>
       <c r="K8">
-        <v>0.512</v>
+        <v>-0.417</v>
       </c>
       <c r="L8">
-        <v>0.005311203319502075</v>
+        <v>-0.1077519379844961</v>
       </c>
       <c r="M8">
-        <v>1.77</v>
+        <v>0.1556</v>
       </c>
       <c r="N8">
-        <v>0.03177737881508079</v>
+        <v>0.009099415204678361</v>
       </c>
       <c r="O8">
-        <v>3.45703125</v>
+        <v>-0.3731414868105515</v>
       </c>
       <c r="P8">
-        <v>1.77</v>
+        <v>0.1556</v>
       </c>
       <c r="Q8">
-        <v>0.03177737881508079</v>
+        <v>0.009099415204678361</v>
       </c>
       <c r="R8">
-        <v>3.45703125</v>
+        <v>-0.3731414868105515</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1377,73 +1353,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>56.9</v>
+        <v>3.71</v>
       </c>
       <c r="V8">
-        <v>1.021543985637343</v>
+        <v>0.2169590643274854</v>
       </c>
       <c r="W8">
-        <v>0.1430167597765363</v>
+        <v>-0.09104803493449781</v>
       </c>
       <c r="X8">
-        <v>0.09053800326417068</v>
+        <v>0.1871631551514467</v>
       </c>
       <c r="Y8">
-        <v>0.05247875651236562</v>
+        <v>-0.2782111900859445</v>
       </c>
       <c r="Z8">
-        <v>-0.9366498251068792</v>
+        <v>0.24791800128123</v>
       </c>
       <c r="AA8">
-        <v>-0.0189467547609794</v>
+        <v>-0.02600896860986547</v>
       </c>
       <c r="AB8">
-        <v>0.09048535040615932</v>
+        <v>0.1345167023816337</v>
       </c>
       <c r="AC8">
-        <v>-0.1094321051671387</v>
+        <v>-0.1605256709914992</v>
       </c>
       <c r="AD8">
-        <v>0.06</v>
+        <v>13.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.06</v>
+        <v>13.3</v>
       </c>
       <c r="AG8">
-        <v>-56.84</v>
+        <v>9.59</v>
       </c>
       <c r="AH8">
-        <v>0.001076040172166427</v>
+        <v>0.4375</v>
       </c>
       <c r="AI8">
-        <v>0.001311188811188811</v>
+        <v>0.7750582750582751</v>
       </c>
       <c r="AJ8">
-        <v>49.8596491228073</v>
+        <v>0.3593106032221806</v>
       </c>
       <c r="AK8">
-        <v>5.102333931777381</v>
+        <v>0.7130111524163569</v>
       </c>
       <c r="AL8">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>0.01214574898785425</v>
-      </c>
-      <c r="AO8">
-        <v>121.875</v>
+        <v>-106.4</v>
       </c>
       <c r="AP8">
-        <v>-11.50607287449393</v>
-      </c>
-      <c r="AQ8">
-        <v>121.875</v>
+        <v>-76.72</v>
       </c>
     </row>
     <row r="9">
@@ -1463,43 +1433,43 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.00868</v>
+        <v>0.006</v>
       </c>
       <c r="G9">
-        <v>0.02039156626506024</v>
+        <v>-0.1139194139194139</v>
       </c>
       <c r="H9">
-        <v>0.02039156626506024</v>
+        <v>-0.1139194139194139</v>
       </c>
       <c r="I9">
-        <v>-0.1216867469879518</v>
+        <v>-0.1684981684981685</v>
       </c>
       <c r="J9">
-        <v>-0.1216867469879518</v>
+        <v>-0.1684981684981685</v>
       </c>
       <c r="K9">
-        <v>-3.84</v>
+        <v>-5.27</v>
       </c>
       <c r="L9">
-        <v>-0.1156626506024096</v>
+        <v>-0.193040293040293</v>
       </c>
       <c r="M9">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="N9">
-        <v>0.03310344827586207</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="O9">
-        <v>-0.375</v>
+        <v>-0.2333965844402277</v>
       </c>
       <c r="P9">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="Q9">
-        <v>0.03310344827586207</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="R9">
-        <v>-0.375</v>
+        <v>-0.2333965844402277</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1508,67 +1478,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>32.6</v>
+        <v>18.6</v>
       </c>
       <c r="V9">
-        <v>0.7494252873563219</v>
+        <v>0.6480836236933799</v>
       </c>
       <c r="W9">
-        <v>-0.03344947735191638</v>
+        <v>-0.04875115633672526</v>
       </c>
       <c r="X9">
-        <v>0.09048319142839241</v>
+        <v>0.136245194877425</v>
       </c>
       <c r="Y9">
-        <v>-0.1239326687803088</v>
+        <v>-0.1849963512141502</v>
       </c>
       <c r="Z9">
-        <v>0.4356955380577429</v>
+        <v>0.36158940397351</v>
       </c>
       <c r="AA9">
-        <v>-0.05301837270341208</v>
+        <v>-0.06092715231788079</v>
       </c>
       <c r="AB9">
-        <v>0.09048319142839241</v>
+        <v>0.1360662388506227</v>
       </c>
       <c r="AC9">
-        <v>-0.1435015641318045</v>
+        <v>-0.1969933911685035</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AG9">
-        <v>-32.6</v>
+        <v>-18.531</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.002398414960547812</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.0008054255331566845</v>
       </c>
       <c r="AJ9">
-        <v>-2.990825688073395</v>
+        <v>-1.822303077982103</v>
       </c>
       <c r="AK9">
-        <v>-0.4317880794701987</v>
+        <v>-0.2762975443200287</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AN9">
-        <v>-0</v>
+        <v>-0.01642857142857143</v>
+      </c>
+      <c r="AO9">
+        <v>-418.1818181818182</v>
       </c>
       <c r="AP9">
-        <v>9.030470914127424</v>
+        <v>4.412142857142857</v>
+      </c>
+      <c r="AQ9">
+        <v>-418.1818181818182</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Padma Islami Life Insurance Limited (DSE:PADMALIFE)</t>
+          <t>Fareast Islami Life Insurance Company Limited (DSE:FAREASTLIF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,109 +1564,109 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.236</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="G10">
-        <v>-0.1342789598108747</v>
+        <v>-2.553431798436142</v>
       </c>
       <c r="H10">
-        <v>-0.1342789598108747</v>
+        <v>-2.553431798436142</v>
       </c>
       <c r="I10">
-        <v>-0.2978723404255319</v>
+        <v>-2.84622067767159</v>
       </c>
       <c r="J10">
-        <v>-0.2978723404255319</v>
+        <v>-2.84622067767159</v>
       </c>
       <c r="K10">
-        <v>-0.453</v>
+        <v>-330.6</v>
       </c>
       <c r="L10">
-        <v>-0.1070921985815603</v>
+        <v>-2.87228496959166</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>0.881</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.0161651376146789</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0.002664851784633999</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>0.881</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.0161651376146789</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0.002664851784633999</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>3.57</v>
+        <v>67.5</v>
       </c>
       <c r="V10">
-        <v>0.1637614678899083</v>
+        <v>1.238532110091743</v>
       </c>
       <c r="W10">
-        <v>-0.09890829694323144</v>
+        <v>-37.5255391600454</v>
       </c>
       <c r="X10">
-        <v>0.1245612350764111</v>
+        <v>0.1467268876672613</v>
       </c>
       <c r="Y10">
-        <v>-0.2234695320196425</v>
-      </c>
-      <c r="Z10">
-        <v>0.2750325097529259</v>
-      </c>
-      <c r="AA10">
-        <v>-0.08192457737321197</v>
+        <v>-37.67226604771267</v>
       </c>
       <c r="AB10">
-        <v>0.0904630853410229</v>
-      </c>
-      <c r="AC10">
-        <v>-0.1723876627142349</v>
+        <v>0.1355867709224965</v>
       </c>
       <c r="AD10">
-        <v>14.6</v>
+        <v>8.83</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>14.6</v>
+        <v>8.83</v>
       </c>
       <c r="AG10">
-        <v>11.03</v>
+        <v>-58.67</v>
       </c>
       <c r="AH10">
-        <v>0.4010989010989011</v>
+        <v>0.1394283909679457</v>
       </c>
       <c r="AI10">
-        <v>0.7612095933263816</v>
+        <v>0.4856985698569857</v>
       </c>
       <c r="AJ10">
-        <v>0.3359731952482485</v>
+        <v>14.06954436450839</v>
       </c>
       <c r="AK10">
-        <v>0.7065983344010249</v>
+        <v>1.189578264395783</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AN10">
-        <v>-16.1504424778761</v>
+        <v>-0.02711083819465766</v>
+      </c>
+      <c r="AO10">
+        <v>-5118.75</v>
       </c>
       <c r="AP10">
-        <v>-12.20132743362832</v>
+        <v>0.1801350936444581</v>
+      </c>
+      <c r="AQ10">
+        <v>-5118.75</v>
       </c>
     </row>
     <row r="11">
@@ -1701,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pragati Life Insurance Limited (DSE:PRAGATILIF)</t>
+          <t>Meghna Life Insurance Company Limited (DSE:MEGHNALIFE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1710,46 +1686,43 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.108</v>
-      </c>
-      <c r="E11">
-        <v>-0.116</v>
+        <v>-0.0185</v>
       </c>
       <c r="G11">
-        <v>0.08329896907216496</v>
+        <v>-0.01993348115299335</v>
       </c>
       <c r="H11">
-        <v>0.08329896907216496</v>
+        <v>-0.01993348115299335</v>
       </c>
       <c r="I11">
-        <v>0.05938144329896907</v>
+        <v>-0.1567627494456763</v>
       </c>
       <c r="J11">
-        <v>0.05222521808088818</v>
+        <v>-0.1567627494456763</v>
       </c>
       <c r="K11">
-        <v>2.4</v>
+        <v>-8.19</v>
       </c>
       <c r="L11">
-        <v>0.04948453608247422</v>
+        <v>-0.1815964523281596</v>
       </c>
       <c r="M11">
-        <v>0.678</v>
+        <v>0.638</v>
       </c>
       <c r="N11">
-        <v>0.0211214953271028</v>
+        <v>0.02407547169811321</v>
       </c>
       <c r="O11">
-        <v>0.2825</v>
+        <v>-0.0778998778998779</v>
       </c>
       <c r="P11">
-        <v>0.678</v>
+        <v>0.638</v>
       </c>
       <c r="Q11">
-        <v>0.0211214953271028</v>
+        <v>0.02407547169811321</v>
       </c>
       <c r="R11">
-        <v>0.2825</v>
+        <v>-0.0778998778998779</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1758,31 +1731,22 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>21.4</v>
+        <v>76.3</v>
       </c>
       <c r="V11">
-        <v>0.6666666666666666</v>
+        <v>2.879245283018868</v>
       </c>
       <c r="W11">
-        <v>1.325966850828729</v>
+        <v>-2.073417721518987</v>
       </c>
       <c r="X11">
-        <v>0.09048319142839241</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="Y11">
-        <v>1.235483659400337</v>
-      </c>
-      <c r="Z11">
-        <v>-1.94077631052421</v>
-      </c>
-      <c r="AA11">
-        <v>-0.1013574660633484</v>
+        <v>-2.209505036372395</v>
       </c>
       <c r="AB11">
-        <v>0.09048319142839241</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1918406574917408</v>
+        <v>0.1360873148534076</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1794,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-21.4</v>
+        <v>-76.3</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1803,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-1.999999999999999</v>
+        <v>1.532128514056225</v>
       </c>
       <c r="AK11">
-        <v>1.267772511848341</v>
+        <v>1.053285477636665</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1815,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP11">
-        <v>-7.062706270627062</v>
+        <v>11.33729569093611</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1793,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>National Life Insurance Company Limited (DSE:NATLIFEINS)</t>
+          <t>Popular Life Insurance Company Limited (DSE:POPULARLIF)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1838,40 +1802,40 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.2349367088607595</v>
+        <v>0.1122940430925222</v>
       </c>
       <c r="H12">
-        <v>0.2349367088607595</v>
+        <v>0.1122940430925222</v>
       </c>
       <c r="I12">
-        <v>0.270379746835443</v>
+        <v>-0.1238276299112801</v>
       </c>
       <c r="J12">
-        <v>0.2475133453887884</v>
+        <v>-0.1238276299112801</v>
       </c>
       <c r="K12">
-        <v>48</v>
+        <v>-10.3</v>
       </c>
       <c r="L12">
-        <v>0.2430379746835443</v>
+        <v>-0.1305449936628644</v>
       </c>
       <c r="M12">
-        <v>4.32</v>
+        <v>2.31</v>
       </c>
       <c r="N12">
-        <v>0.01539558089807555</v>
+        <v>0.06047120418848168</v>
       </c>
       <c r="O12">
-        <v>0.09000000000000001</v>
+        <v>-0.2242718446601942</v>
       </c>
       <c r="P12">
-        <v>4.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q12">
-        <v>0.01539558089807555</v>
+        <v>0.06047120418848168</v>
       </c>
       <c r="R12">
-        <v>0.09000000000000001</v>
+        <v>-0.2242718446601942</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1880,73 +1844,293 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>240.3</v>
+        <v>39.2</v>
       </c>
       <c r="V12">
-        <v>0.8563791874554526</v>
-      </c>
-      <c r="W12">
-        <v>3.037974683544304</v>
+        <v>1.026178010471204</v>
       </c>
       <c r="X12">
-        <v>0.09048319142839241</v>
-      </c>
-      <c r="Y12">
-        <v>2.947491492115911</v>
-      </c>
-      <c r="Z12">
-        <v>-1.015424164524422</v>
-      </c>
-      <c r="AA12">
-        <v>-0.2513310319500551</v>
+        <v>0.1364827037442713</v>
       </c>
       <c r="AB12">
-        <v>0.09048319142839241</v>
-      </c>
-      <c r="AC12">
-        <v>-0.3418142233784475</v>
+        <v>0.136034722649043</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AG12">
-        <v>-240.3</v>
+        <v>-38.97000000000001</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.005984907624251887</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.006419201786212672</v>
       </c>
       <c r="AJ12">
-        <v>-5.962779156327542</v>
+        <v>50.61038961038941</v>
       </c>
       <c r="AK12">
-        <v>1.077578475336323</v>
+        <v>11.56379821958456</v>
       </c>
       <c r="AL12">
-        <v>0.103</v>
+        <v>0.031</v>
       </c>
       <c r="AM12">
-        <v>0.103</v>
+        <v>0.031</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>-0.02519167579408543</v>
       </c>
       <c r="AO12">
-        <v>518.4466019417475</v>
+        <v>-315.1612903225806</v>
       </c>
       <c r="AP12">
-        <v>-4.45</v>
+        <v>4.268346111719606</v>
       </c>
       <c r="AQ12">
-        <v>518.4466019417475</v>
+        <v>-315.1612903225806</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Prime Islami Life Insurance Limited (DSE:PRIMELIFE)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0717</v>
+      </c>
+      <c r="G13">
+        <v>-0.06947162426614481</v>
+      </c>
+      <c r="H13">
+        <v>-0.06947162426614481</v>
+      </c>
+      <c r="I13">
+        <v>-0.1103718199608611</v>
+      </c>
+      <c r="J13">
+        <v>-0.1103718199608611</v>
+      </c>
+      <c r="K13">
+        <v>-7.64</v>
+      </c>
+      <c r="L13">
+        <v>-0.1495107632093933</v>
+      </c>
+      <c r="M13">
+        <v>1.31</v>
+      </c>
+      <c r="N13">
+        <v>0.08291139240506329</v>
+      </c>
+      <c r="O13">
+        <v>-0.1714659685863874</v>
+      </c>
+      <c r="P13">
+        <v>1.31</v>
+      </c>
+      <c r="Q13">
+        <v>0.08291139240506329</v>
+      </c>
+      <c r="R13">
+        <v>-0.1714659685863874</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>8.09</v>
+      </c>
+      <c r="V13">
+        <v>0.5120253164556962</v>
+      </c>
+      <c r="W13">
+        <v>-2.116343490304709</v>
+      </c>
+      <c r="X13">
+        <v>0.1360873148534076</v>
+      </c>
+      <c r="Y13">
+        <v>-2.252430805158117</v>
+      </c>
+      <c r="AB13">
+        <v>0.1360873148534076</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>-8.09</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>-1.049286640726329</v>
+      </c>
+      <c r="AK13">
+        <v>3.236</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>-0</v>
+      </c>
+      <c r="AP13">
+        <v>1.487132352941176</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sunlife Insurance Company Limited (DSE:SUNLIFEINS)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>-0.5245454545454545</v>
+      </c>
+      <c r="H14">
+        <v>-0.5245454545454545</v>
+      </c>
+      <c r="I14">
+        <v>-0.7072727272727273</v>
+      </c>
+      <c r="J14">
+        <v>-0.7072727272727273</v>
+      </c>
+      <c r="K14">
+        <v>-7.85</v>
+      </c>
+      <c r="L14">
+        <v>-0.7136363636363636</v>
+      </c>
+      <c r="M14">
+        <v>0.036</v>
+      </c>
+      <c r="N14">
+        <v>0.001818181818181818</v>
+      </c>
+      <c r="O14">
+        <v>-0.004585987261146496</v>
+      </c>
+      <c r="P14">
+        <v>0.036</v>
+      </c>
+      <c r="Q14">
+        <v>0.001818181818181818</v>
+      </c>
+      <c r="R14">
+        <v>-0.004585987261146496</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>2.69</v>
+      </c>
+      <c r="V14">
+        <v>0.1358585858585858</v>
+      </c>
+      <c r="W14">
+        <v>-1.864608076009501</v>
+      </c>
+      <c r="X14">
+        <v>0.1360873148534076</v>
+      </c>
+      <c r="Y14">
+        <v>-2.000695390862909</v>
+      </c>
+      <c r="AB14">
+        <v>0.1360873148534076</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-2.69</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.1572180011689071</v>
+      </c>
+      <c r="AK14">
+        <v>-3.127906976744186</v>
+      </c>
+      <c r="AL14">
+        <v>0.026</v>
+      </c>
+      <c r="AM14">
+        <v>0.026</v>
+      </c>
+      <c r="AN14">
+        <v>-0</v>
+      </c>
+      <c r="AO14">
+        <v>-299.2307692307692</v>
+      </c>
+      <c r="AP14">
+        <v>0.3788732394366197</v>
+      </c>
+      <c r="AQ14">
+        <v>-299.2307692307692</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0563</v>
+        <v>0.02425</v>
       </c>
       <c r="E2">
-        <v>0.156</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.317602569104715</v>
+        <v>0.1098311023097283</v>
       </c>
       <c r="H2">
-        <v>-0.317602569104715</v>
+        <v>0.1098311023097283</v>
       </c>
       <c r="I2">
-        <v>-0.4187040427383775</v>
+        <v>0.1152579164841861</v>
       </c>
       <c r="J2">
-        <v>-0.3975650605238765</v>
+        <v>0.1092467278138987</v>
       </c>
       <c r="K2">
-        <v>-292.127</v>
+        <v>47.19</v>
       </c>
       <c r="L2">
-        <v>-0.4383790029712777</v>
+        <v>0.08985661785707486</v>
       </c>
       <c r="M2">
-        <v>16.0776</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N2">
-        <v>0.0320782122905028</v>
+        <v>0.02184936614466815</v>
       </c>
       <c r="O2">
-        <v>-0.05503633693564785</v>
+        <v>0.1862682771773681</v>
       </c>
       <c r="P2">
-        <v>16.0776</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.0320782122905028</v>
+        <v>0.02184936614466815</v>
       </c>
       <c r="R2">
-        <v>-0.05503633693564785</v>
+        <v>0.1862682771773681</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>480.79</v>
+        <v>278.809</v>
       </c>
       <c r="V2">
-        <v>0.9592777334397447</v>
+        <v>0.6930375341784738</v>
       </c>
       <c r="W2">
-        <v>-0.06989959563561153</v>
+        <v>-0.1215665730690248</v>
       </c>
       <c r="X2">
-        <v>0.136101406900087</v>
+        <v>0.1260542474844084</v>
       </c>
       <c r="Y2">
-        <v>-0.2060010025356986</v>
+        <v>-0.2476208205534332</v>
       </c>
       <c r="Z2">
-        <v>7.314016024585666</v>
+        <v>6.203137180789493</v>
       </c>
       <c r="AA2">
-        <v>-0.04346806046387313</v>
+        <v>-0.1492452454640704</v>
       </c>
       <c r="AB2">
-        <v>0.13608654480378</v>
+        <v>0.1258594995181622</v>
       </c>
       <c r="AC2">
-        <v>-0.1787595310800013</v>
+        <v>-0.2753330486845405</v>
       </c>
       <c r="AD2">
-        <v>23.417</v>
+        <v>16.01</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.417</v>
+        <v>16.01</v>
       </c>
       <c r="AG2">
-        <v>-457.373</v>
+        <v>-262.799</v>
       </c>
       <c r="AH2">
-        <v>0.0446363728205529</v>
+        <v>0.03827305108651479</v>
       </c>
       <c r="AI2">
-        <v>0.1155841399428422</v>
+        <v>0.09511079427315394</v>
       </c>
       <c r="AJ2">
-        <v>-10.4358728637598</v>
+        <v>-1.883850294979965</v>
       </c>
       <c r="AK2">
-        <v>1.644085221411035</v>
+        <v>2.378723558323301</v>
       </c>
       <c r="AL2">
-        <v>0.283</v>
+        <v>0.453</v>
       </c>
       <c r="AM2">
-        <v>0.283</v>
+        <v>0.453</v>
       </c>
       <c r="AN2">
-        <v>-0.08620759475030833</v>
+        <v>0.244315580650084</v>
       </c>
       <c r="AO2">
-        <v>-985.922261484099</v>
+        <v>133.6203090507726</v>
       </c>
       <c r="AP2">
-        <v>1.683777863677361</v>
+        <v>-4.01036166641233</v>
       </c>
       <c r="AQ2">
-        <v>-985.922261484099</v>
+        <v>133.6203090507726</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3737769080234834</v>
+        <v>0.453551912568306</v>
       </c>
       <c r="H3">
-        <v>0.3737769080234834</v>
+        <v>0.453551912568306</v>
       </c>
       <c r="I3">
-        <v>0.4970645792563601</v>
+        <v>0.51775956284153</v>
       </c>
       <c r="J3">
-        <v>0.4937775392967615</v>
+        <v>0.5036642216428792</v>
       </c>
       <c r="K3">
-        <v>24.6</v>
+        <v>36.1</v>
       </c>
       <c r="L3">
-        <v>0.4814090019569472</v>
+        <v>0.4931693989071038</v>
       </c>
       <c r="M3">
-        <v>0.189</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="N3">
-        <v>0.006872727272727273</v>
+        <v>0.01630813953488372</v>
       </c>
       <c r="O3">
-        <v>0.007682926829268293</v>
+        <v>0.01554016620498615</v>
       </c>
       <c r="P3">
-        <v>0.189</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.006872727272727273</v>
+        <v>0.01630813953488372</v>
       </c>
       <c r="R3">
-        <v>0.007682926829268293</v>
+        <v>0.01554016620498615</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,64 +764,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>15.1</v>
+        <v>24.8</v>
       </c>
       <c r="V3">
-        <v>0.5490909090909091</v>
+        <v>0.7209302325581396</v>
       </c>
       <c r="W3">
-        <v>4.263431542461006</v>
+        <v>7.42798353909465</v>
       </c>
       <c r="X3">
-        <v>0.1384227410679704</v>
+        <v>0.1275872074972279</v>
       </c>
       <c r="Y3">
-        <v>4.125008801393035</v>
+        <v>7.300396331597423</v>
       </c>
       <c r="AB3">
-        <v>0.1360521149800301</v>
+        <v>0.1259948239646817</v>
       </c>
       <c r="AD3">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="AG3">
-        <v>-14.122</v>
+        <v>-23.823</v>
       </c>
       <c r="AH3">
-        <v>0.03434229931877238</v>
+        <v>0.02761681318370693</v>
       </c>
       <c r="AI3">
-        <v>0.1675231243576567</v>
+        <v>0.1800257969412198</v>
       </c>
       <c r="AJ3">
-        <v>-1.055613694124682</v>
+        <v>-2.252339982981942</v>
       </c>
       <c r="AK3">
-        <v>1.524724681494278</v>
+        <v>1.229701130439271</v>
       </c>
       <c r="AL3">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="AM3">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="AN3">
-        <v>0.03595588235294118</v>
+        <v>0.02479695431472081</v>
       </c>
       <c r="AO3">
-        <v>373.5294117647059</v>
+        <v>565.6716417910447</v>
       </c>
       <c r="AP3">
-        <v>-0.5191911764705882</v>
+        <v>-0.6046446700507615</v>
       </c>
       <c r="AQ3">
-        <v>373.5294117647059</v>
+        <v>565.6716417910447</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chartered Life Insurance Company Limited (DSE:CLICL)</t>
+          <t>National Life Insurance Company Limited (DSE:NATLIFEINS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,61 +841,70 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.463</v>
+        <v>0.125</v>
       </c>
       <c r="E4">
-        <v>0.736</v>
+        <v>0.342</v>
       </c>
       <c r="G4">
-        <v>0.2980030721966206</v>
+        <v>0.2385321100917431</v>
       </c>
       <c r="H4">
-        <v>0.2980030721966206</v>
+        <v>0.2385321100917431</v>
       </c>
       <c r="I4">
-        <v>0.2749615975422427</v>
+        <v>0.2334352701325178</v>
       </c>
       <c r="J4">
-        <v>0.2587211756991044</v>
+        <v>0.2167762430246267</v>
       </c>
       <c r="K4">
-        <v>1.61</v>
+        <v>41.4</v>
       </c>
       <c r="L4">
-        <v>0.2473118279569893</v>
+        <v>0.2110091743119266</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>3.92</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02210941906373378</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.09468599033816426</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3.92</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02210941906373378</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.09468599033816426</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.058093626621545</v>
+      </c>
+      <c r="W4">
+        <v>2.741721854304636</v>
       </c>
       <c r="X4">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
+      </c>
+      <c r="Y4">
+        <v>2.6158653999793</v>
       </c>
       <c r="AB4">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -907,25 +916,37 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-187.6</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>18.21359223300974</v>
+      </c>
+      <c r="AK4">
+        <v>1.081268011527377</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>594.8051948051948</v>
+      </c>
       <c r="AP4">
-        <v>0</v>
+        <v>-4.01713062098501</v>
+      </c>
+      <c r="AQ4">
+        <v>594.8051948051948</v>
       </c>
     </row>
     <row r="5">
@@ -936,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Life Insurance Company Limited (DSE:NATLIFEINS)</t>
+          <t>Pragati Life Insurance Limited (DSE:PRAGATILIF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,46 +966,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.125</v>
+        <v>0.152</v>
       </c>
       <c r="E5">
-        <v>0.431</v>
+        <v>-0.2</v>
       </c>
       <c r="G5">
-        <v>0.2900150526843954</v>
+        <v>0.05442307692307692</v>
       </c>
       <c r="H5">
-        <v>0.2900150526843954</v>
+        <v>0.05442307692307692</v>
       </c>
       <c r="I5">
-        <v>0.2553938785750125</v>
+        <v>0.04346153846153845</v>
       </c>
       <c r="J5">
-        <v>0.2326115837248551</v>
+        <v>0.03123021978021978</v>
       </c>
       <c r="K5">
-        <v>48</v>
+        <v>1.5</v>
       </c>
       <c r="L5">
-        <v>0.2408429503261415</v>
+        <v>0.02884615384615385</v>
       </c>
       <c r="M5">
-        <v>8.630000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="N5">
-        <v>0.04568554790894654</v>
+        <v>0.01042483660130719</v>
       </c>
       <c r="O5">
-        <v>0.1797916666666667</v>
+        <v>0.2126666666666667</v>
       </c>
       <c r="P5">
-        <v>8.630000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="Q5">
-        <v>0.04568554790894654</v>
+        <v>0.01042483660130719</v>
       </c>
       <c r="R5">
-        <v>0.1797916666666667</v>
+        <v>0.2126666666666667</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -993,22 +1014,22 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>215</v>
+        <v>14.9</v>
       </c>
       <c r="V5">
-        <v>1.138168343038645</v>
+        <v>0.4869281045751634</v>
       </c>
       <c r="W5">
-        <v>2.823529411764706</v>
+        <v>0.364963503649635</v>
       </c>
       <c r="X5">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="Y5">
-        <v>2.687442096911298</v>
+        <v>0.2391070493242994</v>
       </c>
       <c r="AB5">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1020,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-215</v>
+        <v>-14.9</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1029,28 +1050,22 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>8.237547892720308</v>
+        <v>-0.9490445859872612</v>
       </c>
       <c r="AK5">
-        <v>1.076614922383575</v>
+        <v>1.330357142857143</v>
       </c>
       <c r="AL5">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
-      <c r="AO5">
-        <v>613.2530120481928</v>
-      </c>
       <c r="AP5">
-        <v>-4.174757281553398</v>
-      </c>
-      <c r="AQ5">
-        <v>613.2530120481928</v>
+        <v>-6.15702479338843</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pragati Life Insurance Limited (DSE:PRAGATILIF)</t>
+          <t>Chartered Life Insurance Company Limited (DSE:CLICL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1069,47 +1084,41 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.132</v>
-      </c>
-      <c r="E6">
-        <v>-0.161</v>
-      </c>
       <c r="G6">
-        <v>0.06431535269709543</v>
+        <v>0.2082825822168087</v>
       </c>
       <c r="H6">
-        <v>0.06431535269709543</v>
+        <v>0.2082825822168087</v>
       </c>
       <c r="I6">
-        <v>0.06141078838174274</v>
+        <v>0.1656516443361754</v>
       </c>
       <c r="J6">
-        <v>0.05098211995473406</v>
+        <v>0.1422077251801234</v>
       </c>
       <c r="K6">
-        <v>2.29</v>
+        <v>1.02</v>
       </c>
       <c r="L6">
-        <v>0.0475103734439834</v>
+        <v>0.1242387332521315</v>
       </c>
       <c r="M6">
-        <v>0.327</v>
+        <v>0.075</v>
       </c>
       <c r="N6">
-        <v>0.008493506493506494</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="O6">
-        <v>0.1427947598253275</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="P6">
-        <v>0.327</v>
+        <v>0.075</v>
       </c>
       <c r="Q6">
-        <v>0.008493506493506494</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="R6">
-        <v>0.1427947598253275</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1118,58 +1127,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>16.8</v>
+        <v>0.534</v>
       </c>
       <c r="V6">
-        <v>0.4363636363636364</v>
+        <v>0.02825396825396826</v>
       </c>
       <c r="W6">
-        <v>0.506637168141593</v>
+        <v>0.4573991031390134</v>
       </c>
       <c r="X6">
-        <v>0.1360873148534076</v>
+        <v>0.1278587527748183</v>
       </c>
       <c r="Y6">
-        <v>0.3705498532881853</v>
+        <v>0.3295403503641952</v>
+      </c>
+      <c r="Z6">
+        <v>4.169629253428137</v>
+      </c>
+      <c r="AA6">
+        <v>0.5929534909745118</v>
       </c>
       <c r="AB6">
-        <v>0.1360873148534076</v>
+        <v>0.126550304855038</v>
+      </c>
+      <c r="AC6">
+        <v>0.4664031861194738</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="AG6">
-        <v>-16.8</v>
+        <v>0.08699999999999997</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.03181189488243431</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1540560654924336</v>
       </c>
       <c r="AJ6">
-        <v>-0.7741935483870969</v>
+        <v>0.004582082477484593</v>
       </c>
       <c r="AK6">
-        <v>1.311475409836065</v>
+        <v>0.02487846725764941</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.4112582781456954</v>
+      </c>
+      <c r="AO6">
+        <v>23.05084745762712</v>
       </c>
       <c r="AP6">
-        <v>-5.490196078431373</v>
+        <v>0.05761589403973508</v>
+      </c>
+      <c r="AQ6">
+        <v>23.05084745762712</v>
       </c>
     </row>
     <row r="7">
@@ -1180,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rupali Life Insurance Company Limited (DSE:RUPALILIFE)</t>
+          <t>Sandhani Life Insurance Company Limited (DSE:SANDHANINS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,46 +1213,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0563</v>
-      </c>
-      <c r="E7">
-        <v>-0.119</v>
+        <v>0.0338</v>
       </c>
       <c r="G7">
-        <v>0.155363321799308</v>
+        <v>-0.1092592592592593</v>
       </c>
       <c r="H7">
-        <v>0.155363321799308</v>
+        <v>-0.1092592592592593</v>
       </c>
       <c r="I7">
-        <v>0.09688581314878893</v>
+        <v>-0.03411111111111111</v>
       </c>
       <c r="J7">
-        <v>0.06964730164511625</v>
+        <v>-0.03411111111111111</v>
       </c>
       <c r="K7">
-        <v>1.64</v>
+        <v>-2.08</v>
       </c>
       <c r="L7">
-        <v>0.05674740484429066</v>
+        <v>-0.07703703703703704</v>
       </c>
       <c r="M7">
-        <v>0.371</v>
+        <v>1.29</v>
       </c>
       <c r="N7">
-        <v>0.01592274678111588</v>
+        <v>0.0479553903345725</v>
       </c>
       <c r="O7">
-        <v>0.226219512195122</v>
+        <v>-0.6201923076923077</v>
       </c>
       <c r="P7">
-        <v>0.371</v>
+        <v>1.29</v>
       </c>
       <c r="Q7">
-        <v>0.01592274678111588</v>
+        <v>0.0479553903345725</v>
       </c>
       <c r="R7">
-        <v>0.226219512195122</v>
+        <v>-0.6201923076923077</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1237,58 +1258,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>17.8</v>
+        <v>14.8</v>
       </c>
       <c r="V7">
-        <v>0.7639484978540773</v>
+        <v>0.5501858736059481</v>
       </c>
       <c r="W7">
-        <v>0.1826280623608018</v>
+        <v>-0.02429906542056075</v>
       </c>
       <c r="X7">
-        <v>0.1361154989467665</v>
+        <v>0.1259606631665726</v>
       </c>
       <c r="Y7">
-        <v>0.04651256341403529</v>
+        <v>-0.1502597285871334</v>
+      </c>
+      <c r="Z7">
+        <v>0.4025704871102895</v>
+      </c>
+      <c r="AA7">
+        <v>-0.01373212661587321</v>
       </c>
       <c r="AB7">
-        <v>0.1360857747541524</v>
+        <v>0.1258580623289706</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1395901889448438</v>
       </c>
       <c r="AD7">
-        <v>0.01</v>
+        <v>0.046</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.01</v>
+        <v>0.046</v>
       </c>
       <c r="AG7">
-        <v>-17.79</v>
+        <v>-14.754</v>
       </c>
       <c r="AH7">
-        <v>0.000429000429000429</v>
+        <v>0.00170711793958287</v>
       </c>
       <c r="AI7">
-        <v>0.001310615989515072</v>
+        <v>0.0005909102587159262</v>
       </c>
       <c r="AJ7">
-        <v>-3.228675136116151</v>
+        <v>-1.214720895768155</v>
       </c>
       <c r="AK7">
-        <v>1.749262536873156</v>
+        <v>-0.2340196047330521</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AN7">
-        <v>0.003236245954692557</v>
+        <v>-0.0775716694772344</v>
+      </c>
+      <c r="AO7">
+        <v>-13.15714285714286</v>
       </c>
       <c r="AP7">
-        <v>-5.757281553398058</v>
+        <v>24.88026981450253</v>
+      </c>
+      <c r="AQ7">
+        <v>-13.15714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -1308,100 +1344,97 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.223</v>
+        <v>-0.208</v>
       </c>
       <c r="G8">
-        <v>0.07622739018087854</v>
+        <v>-1.172161172161172</v>
       </c>
       <c r="H8">
-        <v>0.07622739018087854</v>
+        <v>-1.172161172161172</v>
       </c>
       <c r="I8">
-        <v>-0.1049095607235142</v>
+        <v>-1.402930402930403</v>
       </c>
       <c r="J8">
-        <v>-0.1049095607235142</v>
+        <v>-1.402930402930403</v>
       </c>
       <c r="K8">
-        <v>-0.417</v>
+        <v>-3.82</v>
       </c>
       <c r="L8">
-        <v>-0.1077519379844961</v>
+        <v>-1.399267399267399</v>
       </c>
       <c r="M8">
-        <v>0.1556</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.009099415204678361</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.3731414868105515</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0.1556</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.009099415204678361</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0.3731414868105515</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>3.71</v>
+        <v>0.895</v>
       </c>
       <c r="V8">
-        <v>0.2169590643274854</v>
+        <v>0.0613013698630137</v>
       </c>
       <c r="W8">
-        <v>-0.09104803493449781</v>
+        <v>-0.9896373056994818</v>
       </c>
       <c r="X8">
-        <v>0.1871631551514467</v>
+        <v>0.184291608598506</v>
       </c>
       <c r="Y8">
-        <v>-0.2782111900859445</v>
+        <v>-1.173928914297988</v>
       </c>
       <c r="Z8">
-        <v>0.24791800128123</v>
+        <v>0.2029739776951673</v>
       </c>
       <c r="AA8">
-        <v>-0.02600896860986547</v>
+        <v>-0.2847583643122677</v>
       </c>
       <c r="AB8">
-        <v>0.1345167023816337</v>
+        <v>0.1263175441119694</v>
       </c>
       <c r="AC8">
-        <v>-0.1605256709914992</v>
+        <v>-0.4110759084242371</v>
       </c>
       <c r="AD8">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="AG8">
-        <v>9.59</v>
+        <v>13.105</v>
       </c>
       <c r="AH8">
-        <v>0.4375</v>
+        <v>0.4895104895104895</v>
       </c>
       <c r="AI8">
-        <v>0.7750582750582751</v>
+        <v>0.7986309184255561</v>
       </c>
       <c r="AJ8">
-        <v>0.3593106032221806</v>
+        <v>0.4730193105937557</v>
       </c>
       <c r="AK8">
-        <v>0.7130111524163569</v>
+        <v>0.7877968139464983</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1410,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-106.4</v>
+        <v>-3.954802259887006</v>
       </c>
       <c r="AP8">
-        <v>-76.72</v>
+        <v>-3.701977401129944</v>
       </c>
     </row>
     <row r="9">
@@ -1424,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandhani Life Insurance Company Limited (DSE:SANDHANINS)</t>
+          <t>Sunlife Insurance Company Limited (DSE:SUNLIFEINS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1433,118 +1466,115 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.006</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="G9">
-        <v>-0.1139194139194139</v>
+        <v>-0.6522210184182015</v>
       </c>
       <c r="H9">
-        <v>-0.1139194139194139</v>
+        <v>-0.6522210184182015</v>
       </c>
       <c r="I9">
-        <v>-0.1684981684981685</v>
+        <v>-0.7053087757313109</v>
       </c>
       <c r="J9">
-        <v>-0.1684981684981685</v>
+        <v>-0.7053087757313109</v>
       </c>
       <c r="K9">
-        <v>-5.27</v>
+        <v>-6.7</v>
       </c>
       <c r="L9">
-        <v>-0.193040293040293</v>
+        <v>-0.7258938244853738</v>
       </c>
       <c r="M9">
-        <v>1.23</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.04285714285714286</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0.2333965844402277</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1.23</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.04285714285714286</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0.2333965844402277</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>18.6</v>
+        <v>0.89</v>
       </c>
       <c r="V9">
-        <v>0.6480836236933799</v>
+        <v>0.05144508670520231</v>
       </c>
       <c r="W9">
-        <v>-0.04875115633672526</v>
+        <v>-1.59144893111639</v>
       </c>
       <c r="X9">
-        <v>0.136245194877425</v>
+        <v>0.1265292547844857</v>
       </c>
       <c r="Y9">
-        <v>-0.1849963512141502</v>
+        <v>-1.717978185900875</v>
       </c>
       <c r="Z9">
-        <v>0.36158940397351</v>
+        <v>4.245630174793009</v>
       </c>
       <c r="AA9">
-        <v>-0.06092715231788079</v>
+        <v>-2.994480220791168</v>
       </c>
       <c r="AB9">
-        <v>0.1360662388506227</v>
+        <v>0.1259315684038758</v>
       </c>
       <c r="AC9">
-        <v>-0.1969933911685035</v>
+        <v>-3.120411789195044</v>
       </c>
       <c r="AD9">
-        <v>0.06900000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.06900000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="AG9">
-        <v>-18.531</v>
+        <v>-0.6990000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.002398414960547812</v>
+        <v>0.01091990166371277</v>
       </c>
       <c r="AI9">
-        <v>0.0008054255331566845</v>
+        <v>0.05217153783119367</v>
       </c>
       <c r="AJ9">
-        <v>-1.822303077982103</v>
+        <v>-0.04210589723510633</v>
       </c>
       <c r="AK9">
-        <v>-0.2762975443200287</v>
+        <v>-0.2522555034283652</v>
       </c>
       <c r="AL9">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AM9">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AN9">
-        <v>-0.01642857142857143</v>
+        <v>-0.03172757475083057</v>
       </c>
       <c r="AO9">
-        <v>-418.1818181818182</v>
+        <v>-651</v>
       </c>
       <c r="AP9">
-        <v>4.412142857142857</v>
+        <v>0.1161129568106312</v>
       </c>
       <c r="AQ9">
-        <v>-418.1818181818182</v>
+        <v>-651</v>
       </c>
     </row>
     <row r="10">
@@ -1555,7 +1585,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fareast Islami Life Insurance Company Limited (DSE:FAREASTLIF)</t>
+          <t>Meghna Life Insurance Company Limited (DSE:MEGHNALIFE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,43 +1594,43 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.04269999999999999</v>
+        <v>-0.008840000000000001</v>
       </c>
       <c r="G10">
-        <v>-2.553431798436142</v>
+        <v>-0.1341573033707865</v>
       </c>
       <c r="H10">
-        <v>-2.553431798436142</v>
+        <v>-0.1341573033707865</v>
       </c>
       <c r="I10">
-        <v>-2.84622067767159</v>
+        <v>-0.1622471910112359</v>
       </c>
       <c r="J10">
-        <v>-2.84622067767159</v>
+        <v>-0.1622471910112359</v>
       </c>
       <c r="K10">
-        <v>-330.6</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L10">
-        <v>-2.87228496959166</v>
+        <v>-0.1903370786516854</v>
       </c>
       <c r="M10">
-        <v>0.881</v>
+        <v>0.644</v>
       </c>
       <c r="N10">
-        <v>0.0161651376146789</v>
+        <v>0.0207741935483871</v>
       </c>
       <c r="O10">
-        <v>-0.002664851784633999</v>
+        <v>-0.07603305785123966</v>
       </c>
       <c r="P10">
-        <v>0.881</v>
+        <v>0.644</v>
       </c>
       <c r="Q10">
-        <v>0.0161651376146789</v>
+        <v>0.0207741935483871</v>
       </c>
       <c r="R10">
-        <v>-0.002664851784633999</v>
+        <v>-0.07603305785123966</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1609,64 +1639,64 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.238532110091743</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>-37.5255391600454</v>
+        <v>-2.211488250652742</v>
       </c>
       <c r="X10">
-        <v>0.1467268876672613</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="Y10">
-        <v>-37.67226604771267</v>
+        <v>-2.337344704978078</v>
       </c>
       <c r="AB10">
-        <v>0.1355867709224965</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="AD10">
-        <v>8.83</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8.83</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>-58.67</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>0.1394283909679457</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.4856985698569857</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>14.06954436450839</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.189578264395783</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>0.064</v>
+        <v>0.005</v>
       </c>
       <c r="AM10">
-        <v>0.064</v>
+        <v>0.005</v>
       </c>
       <c r="AN10">
-        <v>-0.02711083819465766</v>
+        <v>-0</v>
       </c>
       <c r="AO10">
-        <v>-5118.75</v>
+        <v>-1444</v>
       </c>
       <c r="AP10">
-        <v>0.1801350936444581</v>
+        <v>-0</v>
       </c>
       <c r="AQ10">
-        <v>-5118.75</v>
+        <v>-1444</v>
       </c>
     </row>
     <row r="11">
@@ -1677,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meghna Life Insurance Company Limited (DSE:MEGHNALIFE)</t>
+          <t>Prime Islami Life Insurance Limited (DSE:PRIMELIFE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1686,43 +1716,43 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0185</v>
+        <v>0.0276</v>
       </c>
       <c r="G11">
-        <v>-0.01993348115299335</v>
+        <v>-0.05570291777188328</v>
       </c>
       <c r="H11">
-        <v>-0.01993348115299335</v>
+        <v>-0.05570291777188328</v>
       </c>
       <c r="I11">
-        <v>-0.1567627494456763</v>
+        <v>-0.02437665782493369</v>
       </c>
       <c r="J11">
-        <v>-0.1567627494456763</v>
+        <v>-0.02437665782493369</v>
       </c>
       <c r="K11">
-        <v>-8.19</v>
+        <v>-2</v>
       </c>
       <c r="L11">
-        <v>-0.1815964523281596</v>
+        <v>-0.05305039787798408</v>
       </c>
       <c r="M11">
-        <v>0.638</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N11">
-        <v>0.02407547169811321</v>
+        <v>0.004829931972789116</v>
       </c>
       <c r="O11">
-        <v>-0.0778998778998779</v>
+        <v>-0.0355</v>
       </c>
       <c r="P11">
-        <v>0.638</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q11">
-        <v>0.02407547169811321</v>
+        <v>0.004829931972789116</v>
       </c>
       <c r="R11">
-        <v>-0.0778998778998779</v>
+        <v>-0.0355</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,22 +1761,22 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>76.3</v>
+        <v>3.29</v>
       </c>
       <c r="V11">
-        <v>2.879245283018868</v>
+        <v>0.2238095238095238</v>
       </c>
       <c r="W11">
-        <v>-2.073417721518987</v>
+        <v>-1.020408163265306</v>
       </c>
       <c r="X11">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="Y11">
-        <v>-2.209505036372395</v>
+        <v>-1.146264617590642</v>
       </c>
       <c r="AB11">
-        <v>0.1360873148534076</v>
+        <v>0.1258564543253356</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1758,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-76.3</v>
+        <v>-3.29</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1767,22 +1797,28 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1.532128514056225</v>
+        <v>-0.2883435582822086</v>
       </c>
       <c r="AK11">
-        <v>1.053285477636665</v>
+        <v>-7.000000000000004</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AN11">
         <v>-0</v>
       </c>
+      <c r="AO11">
+        <v>-6.294520547945206</v>
+      </c>
       <c r="AP11">
-        <v>11.33729569093611</v>
+        <v>4.180432020330368</v>
+      </c>
+      <c r="AQ11">
+        <v>-6.294520547945206</v>
       </c>
     </row>
     <row r="12">
@@ -1801,41 +1837,44 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.0209</v>
+      </c>
       <c r="G12">
-        <v>0.1122940430925222</v>
+        <v>-0.08897849462365591</v>
       </c>
       <c r="H12">
-        <v>0.1122940430925222</v>
+        <v>-0.08897849462365591</v>
       </c>
       <c r="I12">
-        <v>-0.1238276299112801</v>
+        <v>-0.0993279569892473</v>
       </c>
       <c r="J12">
-        <v>-0.1238276299112801</v>
+        <v>-0.0993279569892473</v>
       </c>
       <c r="K12">
-        <v>-10.3</v>
+        <v>-9.76</v>
       </c>
       <c r="L12">
-        <v>-0.1305449936628644</v>
+        <v>-0.1311827956989247</v>
       </c>
       <c r="M12">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="N12">
-        <v>0.06047120418848168</v>
+        <v>0.05218579234972677</v>
       </c>
       <c r="O12">
-        <v>-0.2242718446601942</v>
+        <v>-0.1956967213114754</v>
       </c>
       <c r="P12">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="Q12">
-        <v>0.06047120418848168</v>
+        <v>0.05218579234972677</v>
       </c>
       <c r="R12">
-        <v>-0.2242718446601942</v>
+        <v>-0.1956967213114754</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1844,293 +1883,64 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>39.2</v>
+        <v>31.1</v>
       </c>
       <c r="V12">
-        <v>1.026178010471204</v>
+        <v>0.8497267759562842</v>
+      </c>
+      <c r="W12">
+        <v>-0.2188340807174888</v>
       </c>
       <c r="X12">
-        <v>0.1364827037442713</v>
+        <v>0.1261478318022441</v>
+      </c>
+      <c r="Y12">
+        <v>-0.3449819125197329</v>
       </c>
       <c r="AB12">
-        <v>0.136034722649043</v>
+        <v>0.1258609367073538</v>
       </c>
       <c r="AD12">
-        <v>0.23</v>
+        <v>0.175</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.23</v>
+        <v>0.175</v>
       </c>
       <c r="AG12">
-        <v>-38.97000000000001</v>
+        <v>-30.925</v>
       </c>
       <c r="AH12">
-        <v>0.005984907624251887</v>
+        <v>0.004758667573079537</v>
       </c>
       <c r="AI12">
-        <v>0.006419201786212672</v>
+        <v>0.00509090909090909</v>
       </c>
       <c r="AJ12">
-        <v>50.61038961038941</v>
+        <v>-5.449339207048458</v>
       </c>
       <c r="AK12">
-        <v>11.56379821958456</v>
+        <v>-9.442748091603047</v>
       </c>
       <c r="AL12">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="AM12">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="AN12">
-        <v>-0.02519167579408543</v>
+        <v>-0.02643504531722054</v>
       </c>
       <c r="AO12">
-        <v>-315.1612903225806</v>
+        <v>-388.9473684210526</v>
       </c>
       <c r="AP12">
-        <v>4.268346111719606</v>
+        <v>4.671450151057402</v>
       </c>
       <c r="AQ12">
-        <v>-315.1612903225806</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Prime Islami Life Insurance Limited (DSE:PRIMELIFE)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0717</v>
-      </c>
-      <c r="G13">
-        <v>-0.06947162426614481</v>
-      </c>
-      <c r="H13">
-        <v>-0.06947162426614481</v>
-      </c>
-      <c r="I13">
-        <v>-0.1103718199608611</v>
-      </c>
-      <c r="J13">
-        <v>-0.1103718199608611</v>
-      </c>
-      <c r="K13">
-        <v>-7.64</v>
-      </c>
-      <c r="L13">
-        <v>-0.1495107632093933</v>
-      </c>
-      <c r="M13">
-        <v>1.31</v>
-      </c>
-      <c r="N13">
-        <v>0.08291139240506329</v>
-      </c>
-      <c r="O13">
-        <v>-0.1714659685863874</v>
-      </c>
-      <c r="P13">
-        <v>1.31</v>
-      </c>
-      <c r="Q13">
-        <v>0.08291139240506329</v>
-      </c>
-      <c r="R13">
-        <v>-0.1714659685863874</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>8.09</v>
-      </c>
-      <c r="V13">
-        <v>0.5120253164556962</v>
-      </c>
-      <c r="W13">
-        <v>-2.116343490304709</v>
-      </c>
-      <c r="X13">
-        <v>0.1360873148534076</v>
-      </c>
-      <c r="Y13">
-        <v>-2.252430805158117</v>
-      </c>
-      <c r="AB13">
-        <v>0.1360873148534076</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>-8.09</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>-1.049286640726329</v>
-      </c>
-      <c r="AK13">
-        <v>3.236</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>-0</v>
-      </c>
-      <c r="AP13">
-        <v>1.487132352941176</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sunlife Insurance Company Limited (DSE:SUNLIFEINS)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>-0.5245454545454545</v>
-      </c>
-      <c r="H14">
-        <v>-0.5245454545454545</v>
-      </c>
-      <c r="I14">
-        <v>-0.7072727272727273</v>
-      </c>
-      <c r="J14">
-        <v>-0.7072727272727273</v>
-      </c>
-      <c r="K14">
-        <v>-7.85</v>
-      </c>
-      <c r="L14">
-        <v>-0.7136363636363636</v>
-      </c>
-      <c r="M14">
-        <v>0.036</v>
-      </c>
-      <c r="N14">
-        <v>0.001818181818181818</v>
-      </c>
-      <c r="O14">
-        <v>-0.004585987261146496</v>
-      </c>
-      <c r="P14">
-        <v>0.036</v>
-      </c>
-      <c r="Q14">
-        <v>0.001818181818181818</v>
-      </c>
-      <c r="R14">
-        <v>-0.004585987261146496</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2.69</v>
-      </c>
-      <c r="V14">
-        <v>0.1358585858585858</v>
-      </c>
-      <c r="W14">
-        <v>-1.864608076009501</v>
-      </c>
-      <c r="X14">
-        <v>0.1360873148534076</v>
-      </c>
-      <c r="Y14">
-        <v>-2.000695390862909</v>
-      </c>
-      <c r="AB14">
-        <v>0.1360873148534076</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>-2.69</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>-0.1572180011689071</v>
-      </c>
-      <c r="AK14">
-        <v>-3.127906976744186</v>
-      </c>
-      <c r="AL14">
-        <v>0.026</v>
-      </c>
-      <c r="AM14">
-        <v>0.026</v>
-      </c>
-      <c r="AN14">
-        <v>-0</v>
-      </c>
-      <c r="AO14">
-        <v>-299.2307692307692</v>
-      </c>
-      <c r="AP14">
-        <v>0.3788732394366197</v>
-      </c>
-      <c r="AQ14">
-        <v>-299.2307692307692</v>
+        <v>-388.9473684210526</v>
       </c>
     </row>
   </sheetData>
